--- a/data/trans_orig/P32B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456355</t>
+          <t>456383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468259</t>
+          <t>468148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165599</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167535</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>624182</t>
+          <t>625190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635714</t>
+          <t>636502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13546</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23076</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1044872</t>
+          <t>1044086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1055055</t>
+          <t>1055038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>518691</t>
+          <t>518471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>529714</t>
+          <t>529950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1568196</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1582860</t>
+          <t>1582559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343317</t>
+          <t>343101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187347</t>
+          <t>187897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534261</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543627</t>
+          <t>543621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4583</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18108</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>16469</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>36675</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16261</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>15956</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>35383</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1855169</t>
+          <t>1855208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1871384</t>
+          <t>1870699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>876412</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>889937</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2737764</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2757970</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>878259</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>890459</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2739056</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2758483</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23851</t>
+          <t>23687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>487767</t>
+          <t>487931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504860</t>
+          <t>505084</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225348</t>
+          <t>224883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715867</t>
+          <t>716758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734357</t>
+          <t>734372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>24905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48593</t>
+          <t>50290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31454</t>
+          <t>31868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56872</t>
+          <t>57045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1150175</t>
+          <t>1148478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1172649</t>
+          <t>1173863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>581175</t>
+          <t>580904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591075</t>
+          <t>591748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1735843</t>
+          <t>1735670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1761261</t>
+          <t>1760847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308077</t>
+          <t>307921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322288</t>
+          <t>322446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222484</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224607</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>531435</t>
+          <t>533022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547072</t>
+          <t>546961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44572</t>
+          <t>44069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77177</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51484</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86561</t>
+          <t>84876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1959404</t>
+          <t>1961358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1992009</t>
+          <t>1992512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1034300</t>
+          <t>1034215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1045694</t>
+          <t>1045620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2998757</t>
+          <t>3000442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3033834</t>
+          <t>3034272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340509</t>
+          <t>340793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>354652</t>
+          <t>354558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129659</t>
+          <t>129678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>473116</t>
+          <t>474152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488829</t>
+          <t>488720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15543</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35697</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44800</t>
+          <t>44717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1219653</t>
+          <t>1219468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1239807</t>
+          <t>1240155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>711678</t>
+          <t>712236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>723129</t>
+          <t>723080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1937448</t>
+          <t>1937531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1959925</t>
+          <t>1960436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362016</t>
+          <t>361219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374487</t>
+          <t>373832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273011</t>
+          <t>271877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279707</t>
+          <t>279700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>637670</t>
+          <t>637886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652421</t>
+          <t>652338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>30571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56742</t>
+          <t>57869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41558</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71759</t>
+          <t>70203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1935153</t>
+          <t>1934026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1960495</t>
+          <t>1961324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1122153</t>
+          <t>1122800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1136046</t>
+          <t>1136844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3062840</t>
+          <t>3064396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3093041</t>
+          <t>3094772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023 (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21692</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221564</t>
+          <t>220549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236703</t>
+          <t>236642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287630</t>
+          <t>287352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>303395</t>
+          <t>302844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>35478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>956940</t>
+          <t>959389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>977339</t>
+          <t>977608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>689291</t>
+          <t>688396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>705577</t>
+          <t>705223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1656605</t>
+          <t>1656679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1679966</t>
+          <t>1680087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>331953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>341610</t>
+          <t>341405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237590</t>
+          <t>238171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244154</t>
+          <t>244148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572943</t>
+          <t>573584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584201</t>
+          <t>584886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62497</t>
+          <t>60576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1526028</t>
+          <t>1526102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1550973</t>
+          <t>1551180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997793</t>
+          <t>998182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1015430</t>
+          <t>1015354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2530021</t>
+          <t>2531942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2561957</t>
+          <t>2562806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456383</t>
+          <t>456683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468148</t>
+          <t>468291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>625190</t>
+          <t>623888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>636502</t>
+          <t>635772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1044086</t>
+          <t>1043775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1055038</t>
+          <t>1054819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>518471</t>
+          <t>517918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>529950</t>
+          <t>529672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1566268</t>
+          <t>1567698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1582559</t>
+          <t>1582959</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343101</t>
+          <t>342480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187897</t>
+          <t>187024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>533620</t>
+          <t>534278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543621</t>
+          <t>543616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17607</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>16605</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>36431</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18108</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>36675</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1855208</t>
+          <t>1855499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1870699</t>
+          <t>1871485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>876913</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>889594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2738008</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2757834</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>876412</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>889937</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2737764</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2757970</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>487931</t>
+          <t>486499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505084</t>
+          <t>504719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224883</t>
+          <t>224526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>716758</t>
+          <t>714657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734372</t>
+          <t>733925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>27296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>50617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31868</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57045</t>
+          <t>56170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1148478</t>
+          <t>1148151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1173863</t>
+          <t>1171472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>580904</t>
+          <t>581331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591748</t>
+          <t>591061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1735670</t>
+          <t>1736545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1760847</t>
+          <t>1761333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>18293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307921</t>
+          <t>307903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322446</t>
+          <t>322404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>533022</t>
+          <t>532119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546961</t>
+          <t>547522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>44346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>79059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>48703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84876</t>
+          <t>83926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1961358</t>
+          <t>1957522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1992512</t>
+          <t>1992235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1034215</t>
+          <t>1033964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1045620</t>
+          <t>1045635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3000442</t>
+          <t>3001392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3034272</t>
+          <t>3036615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340793</t>
+          <t>340296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>354558</t>
+          <t>354104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129678</t>
+          <t>130285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474152</t>
+          <t>474628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488720</t>
+          <t>488946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>36248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44717</t>
+          <t>47010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1219468</t>
+          <t>1219102</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1240155</t>
+          <t>1239032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>712236</t>
+          <t>712354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>723080</t>
+          <t>723115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1937531</t>
+          <t>1935238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1960436</t>
+          <t>1959780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>361219</t>
+          <t>360586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>373832</t>
+          <t>373754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271877</t>
+          <t>272721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279700</t>
+          <t>279695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>637886</t>
+          <t>637907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652338</t>
+          <t>652533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>57343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>41721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70203</t>
+          <t>69451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1934026</t>
+          <t>1934552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1961324</t>
+          <t>1961395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1122800</t>
+          <t>1122850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1136844</t>
+          <t>1136386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3064396</t>
+          <t>3065148</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3094772</t>
+          <t>3092878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>231238</t>
+          <t>244979</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220549</t>
+          <t>236607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236642</t>
+          <t>250412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,27 +5685,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>297717</t>
+          <t>319025</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287352</t>
+          <t>310625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302844</t>
+          <t>324986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35478</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>971140</t>
+          <t>1029639</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>959389</t>
+          <t>1016253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>977608</t>
+          <t>1036921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>699095</t>
+          <t>546284</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>688396</t>
+          <t>534822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>705223</t>
+          <t>551884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1670236</t>
+          <t>1575923</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1656679</t>
+          <t>1560863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1680087</t>
+          <t>1586255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>983868</t>
+          <t>1044595</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>983868</t>
+          <t>1044595</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>983868</t>
+          <t>1044595</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>708289</t>
+          <t>557864</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>708289</t>
+          <t>557864</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>708289</t>
+          <t>557864</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1692157</t>
+          <t>1602459</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1692157</t>
+          <t>1602459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1692157</t>
+          <t>1602459</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>338053</t>
+          <t>359367</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>331953</t>
+          <t>350756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>341405</t>
+          <t>363986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>264451</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238171</t>
+          <t>259007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244148</t>
+          <t>267075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>580094</t>
+          <t>623818</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>573584</t>
+          <t>615547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584886</t>
+          <t>628896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>245519</t>
+          <t>269127</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>245519</t>
+          <t>269127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>245519</t>
+          <t>269127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>589772</t>
+          <t>637156</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>589772</t>
+          <t>637156</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>589772</t>
+          <t>637156</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>53057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>40293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60576</t>
+          <t>72707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1540430</t>
+          <t>1633985</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1526102</t>
+          <t>1617294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1551180</t>
+          <t>1645418</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1007616</t>
+          <t>884780</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>998182</t>
+          <t>872289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1015354</t>
+          <t>891556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2548046</t>
+          <t>2518765</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2531942</t>
+          <t>2499568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2562806</t>
+          <t>2531982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1571377</t>
+          <t>1670351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1571377</t>
+          <t>1670351</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1571377</t>
+          <t>1670351</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1021141</t>
+          <t>901924</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1021141</t>
+          <t>901924</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1021141</t>
+          <t>901924</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2592518</t>
+          <t>2572275</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2592518</t>
+          <t>2572275</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2592518</t>
+          <t>2572275</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
